--- a/output/ValueSet-vs-presenting-complaint.xlsx
+++ b/output/ValueSet-vs-presenting-complaint.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Presenting Complaints ValueSet</t>
+    <t>Presenting Complaint</t>
   </si>
   <si>
     <t>Status</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Presenting Complaint codes</t>
+    <t>The Presenting Complaint value set includes codes for the presenting complaint in an ED presentation.</t>
   </si>
   <si>
     <t>Purpose</t>
